--- a/owp/owp-2108-live/cortex output files/OWP_2108_JCR_Cortex_v2.xlsx
+++ b/owp/owp-2108-live/cortex output files/OWP_2108_JCR_Cortex_v2.xlsx
@@ -36,12 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="284">
   <si>
     <t xml:space="preserve">OWP #2108 · R&amp;G Apartments</t>
   </si>
   <si>
-    <t xml:space="preserve">Braseth · 263 units · CANCELLED</t>
+    <t xml:space="preserve">Braseth · 263 units · ON HOLD · Summer 2026?</t>
   </si>
   <si>
     <t xml:space="preserve">Forecast at Completion (Revised Basis)</t>
@@ -98,64 +98,334 @@
     <t xml:space="preserve">AR</t>
   </si>
   <si>
-    <t xml:space="preserve">Job Information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job ID</t>
+    <t xml:space="preserve">PROJECT TEAM · KEY PLAYERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-construction. Project on hold pending Braseth go-ahead for Summer 2026 start. Team data from index.html PROJECT_TEAMS + JDR identity block.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Contractor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braseth Construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC Project Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD (Braseth) — primary contact pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Estimator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeffrey S. Gerard / Jordan E. Gerard (takeoff)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Signatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Donelson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEP / Plumbing Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD (Franklin Engineering involved per AP — design fees $90.6k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard (COI) — non-Wrap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON HOLD · Summer 2026?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR Billed to Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$91,402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Cost (sunk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$117,162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrying Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(25,760)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOB #2108 · PROJECT INFORMATION &amp; KEY PLAYERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-construction record — project is on-hold. Team data sourced from index.html PROJECT_TEAMS['2108'] + Sage JDR identity block. GDrive folder not created yet (will populate when Braseth confirms start).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDENTITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Number</t>
   </si>
   <si>
     <t xml:space="preserve">2108</t>
   </si>
   <si>
-    <t xml:space="preserve">Project name</t>
+    <t xml:space="preserve">Job Name</t>
   </si>
   <si>
     <t xml:space="preserve">R&amp;G Apartments</t>
   </si>
   <si>
-    <t xml:space="preserve">General contractor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braseth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expected completion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEP Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELLED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JDR report date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apr 3, 2026</t>
+    <t xml:space="preserve">Project Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-family apartments (pre-construction · on-hold)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-permit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCHEDULE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design / Takeoff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete (Apr 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1 2027 (estimated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design/takeoff complete · awaiting Braseth go-ahead · est. start Summer 2026 / Q1 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINANCIAL POSTURE (PRE-CONSTRUCTION)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not yet executed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revised Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retainage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0 (no AR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lien Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not yet recorded — no AR billed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warranty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending project activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract on File</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not yet executed — Braseth has not committed start date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCOPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plumbing Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Fixtures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD (no fixture schedule yet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixture Counts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — GENERAL CONTRACTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC Superintendent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC Project Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — OWP STAFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Roughin Foreman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD · project on hold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Trim Foreman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Estimator (takeoff)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — OWNER &amp; DEVELOPMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner of Record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — DESIGN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structural Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Civil Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landscape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCUMENT META (current)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay Apps (filed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executed COs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Submittals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permit Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (pre-permit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project hasn't reached document-generation phase. Only the OWP estimating team has touched the file (takeoff + design coordination).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA SOURCES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JDR PDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2108 Job Detail Report (Sage Timberline · Apr 3 2026 run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsed Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2108_data.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboard Arrays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2108_dashboard_arrays.json (16 arrays sourced from index.html PROJECTS['2108'])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDrive Folder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not yet created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDrive Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No GDrive folder created yet (project hasn't reached active stage). All team data from index.html PROJECT_TEAMS['2108'] + Sage JDR identity block.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISK FLAGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrying $91k design cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP has $117k of sunk costs. If project cancels, OWP eats the design + takeoff time. Reach out to Braseth PM to confirm summer 2026 start before Q4 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top-vendor concentration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franklin Engineering = 92.5% of $97k AP. All design fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New GC (Braseth)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP has no closed-job history with Braseth. Once project activates, watch payment cadence + change-order behavior closely.</t>
   </si>
   <si>
     <t xml:space="preserve">Contract Summary</t>
@@ -428,40 +698,94 @@
     <t xml:space="preserve">Hours per unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Predictive Signals (cancelled project)</t>
+    <t xml:space="preserve">Predictive Signals — Job #2108 (pre-construction)</t>
   </si>
   <si>
     <t xml:space="preserve">Signal</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering/Plans (601) unbudgeted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ WATCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No revised budget but $106,488 actual spend — needs CO or budget transfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top vendor concentration (Franklin Engineering)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93% of AP ($90,629) — high, monitor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retention aging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✓ OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0 held · 0.0% of billed · zero (cancelled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0% forecast margin — monitor</t>
+    <t xml:space="preserve">Current Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVA Critical Flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEALTHY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BVA Over Flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Order Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELEVATED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WATCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunk design cost (carrying)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR billed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;$1M for medium job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay apps filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&gt;=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC closed-job history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 jobs with Braseth</t>
   </si>
   <si>
     <t xml:space="preserve">JDR Reconciliation</t>
@@ -555,6 +879,15 @@
   </si>
   <si>
     <t xml:space="preserve">Initial build for #2108 cancelled project. 17-tab JCR schema on revised budget basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1.1 · enriched</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enriched Job Info tab with 11-section sectioned layout (identity / schedule / financial posture / scope / project team — 4 sub-sections / document meta / data sources / risk flags). Corrected status from 'CANCELLED' (template default) to 'ON HOLD · Summer 2026?'. Predictive Signals expanded with pre-construction-specific signals.</t>
   </si>
 </sst>
 </file>
@@ -569,7 +902,7 @@
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,9 +934,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="9"/>
-      <color rgb="FF70655C"/>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF9A4F02"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -655,14 +988,61 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF6B6B6B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF2C2B29"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF70655C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -672,28 +1052,80 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2C2B29"/>
-        <bgColor rgb="FF333300"/>
+        <bgColor rgb="FF1F1F1F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8CEC3"/>
-        <bgColor rgb="FFD5DEC5"/>
+        <fgColor rgb="FFECF0F1"/>
+        <bgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5DEC5"/>
-        <bgColor rgb="FFE8CEC3"/>
+        <fgColor rgb="FF2C3E50"/>
+        <bgColor rgb="FF2C2B29"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E7"/>
+        <bgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD1ECF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF8E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1ECF1"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD5D8DC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD5D8DC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD5D8DC"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5D8DC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -737,24 +1169,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -778,12 +1214,72 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -792,6 +1288,10 @@
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -826,16 +1326,48 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -864,15 +1396,15 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFB8AE"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF70655C"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFF3CD"/>
+      <rgbColor rgb="FFD1ECF1"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD5DEC5"/>
+      <rgbColor rgb="FFD5D8DC"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -882,28 +1414,28 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFECF0F1"/>
+      <rgbColor rgb="FFD4EDDA"/>
+      <rgbColor rgb="FFFFF8E7"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFE8CEC3"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF70655C"/>
+      <rgbColor rgb="FF6B6B6B"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF1F1F1F"/>
+      <rgbColor rgb="FF9A4F02"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF2C3E50"/>
       <rgbColor rgb="FF2C2B29"/>
     </indexedColors>
   </colors>
@@ -1090,156 +1622,526 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <f aca="false">B5-B6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <f aca="false">IFERROR(B7/B5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>91402</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <f aca="false">B11-B12</f>
         <v>91402</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <f aca="false">B5-B11</f>
         <v>-91402</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <f aca="false">IFERROR(B11/B5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="10" t="n">
         <v>15858.75</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="10" t="n">
         <v>97953.1</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="10" t="n">
         <v>3350.12</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="10" t="n">
         <v>-91402</v>
       </c>
     </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="12"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="12"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="12"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="12"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="12"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="12"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="12"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1258,68 +2160,68 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="16" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="33" t="n">
         <v>20.5</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>1414</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="34" t="n">
         <f aca="false">IFERROR(C4/B4,0)</f>
         <v>68.9756097560976</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="16" t="n">
+      <c r="E4" s="5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>720</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="34" t="n">
         <f aca="false">IFERROR(C5/B5,0)</f>
         <v>60</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>109</v>
+      <c r="E5" s="5" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -1341,102 +2243,102 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="33" t="n">
         <v>32.5</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>2134</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="28" t="n">
         <f aca="false">IFERROR(C4/SUM(C$4:C$7),0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="28" t="n">
         <f aca="false">IFERROR(C5/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
         <f aca="false">IFERROR(C6/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
         <f aca="false">IFERROR(C7/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
@@ -1460,52 +2362,52 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="16" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="33" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="18" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="35" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="16" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="33" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="19" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="36" t="n">
         <v>2812.37</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1528,85 +2430,85 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="20" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="37" t="n">
         <v>0.34</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="28" t="n">
         <f aca="false">B4-C4</f>
         <v>-0.34</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="20" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="37" t="n">
         <v>0.45</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="28" t="n">
         <f aca="false">B5-C5</f>
         <v>-0.45</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="20" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" s="37" t="n">
         <v>0.925225949969935</v>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="37" t="n">
         <v>0.38</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="28" t="n">
         <f aca="false">B6-C6</f>
         <v>0.545225949969935</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="16" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" s="33" t="n">
         <v>0.123574144486692</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="33" t="n">
         <v>95</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="38" t="n">
         <f aca="false">B7-C7</f>
         <v>-94.8764258555133</v>
       </c>
@@ -1627,73 +2529,367 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>141</v>
-      </c>
+      <c r="B9" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>242</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>244</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="F12" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1714,91 +2910,91 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="5" t="n">
+      <c r="B3" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>117161.97</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>117161.97</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <f aca="false">IF(ISNUMBER(B4),B4-C4,"—")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="5" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>-91402</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>91402</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="10" t="n">
         <f aca="false">IF(ISNUMBER(B5),B5-C5,"—")</f>
         <v>-182804</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="5" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>97953.1</v>
       </c>
-      <c r="D6" s="9" t="str">
+      <c r="D6" s="10" t="str">
         <f aca="false">IF(ISNUMBER(B6),B6-C6,"—")</f>
         <v>—</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="5" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>3350.12</v>
       </c>
-      <c r="D7" s="9" t="str">
+      <c r="D7" s="10" t="str">
         <f aca="false">IF(ISNUMBER(B7),B7-C7,"—")</f>
         <v>—</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="5" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="6" t="n">
         <v>15858.75</v>
       </c>
-      <c r="D8" s="9" t="str">
+      <c r="D8" s="10" t="str">
         <f aca="false">IF(ISNUMBER(B8),B8-C8,"—")</f>
         <v>—</v>
       </c>
@@ -1822,91 +3018,91 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>165</v>
+      <c r="B5" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="46" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="46" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -1925,39 +3121,50 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>172</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -1976,115 +3183,900 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>263</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="B37" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="B38" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="B46" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="B53" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="B55" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="25"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B62" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B65" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="B66" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C71" s="22"/>
+      <c r="D71" s="22"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="22"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C72" s="22"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+    </row>
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C77" s="25"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C78" s="25"/>
+      <c r="D78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B79" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
     </row>
   </sheetData>
+  <mergeCells count="68">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B79:F79"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2103,90 +4095,90 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10" t="n">
         <f aca="false">C4-B4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="n">
         <f aca="false">C5-B5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="6" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="7" t="n">
         <f aca="false">SUM(B4:B5)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <f aca="false">SUM(C4:C5)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <f aca="false">SUM(D4:D5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>51</v>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2208,36 +4200,36 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>59</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2259,33 +4251,33 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>36</v>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2307,235 +4299,235 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>2134.5</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <f aca="false">D4-E4</f>
         <v>-2134.5</v>
       </c>
-      <c r="G4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="12" t="n">
+      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="28" t="n">
         <f aca="false">IFERROR(E4/D4,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>106487.5</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="10" t="n">
         <f aca="false">D5-E5</f>
         <v>-106487.5</v>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="12" t="n">
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="28" t="n">
         <f aca="false">IFERROR(E5/D5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>922.35</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <f aca="false">D6-E6</f>
         <v>-922.35</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="12" t="n">
+      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
         <f aca="false">IFERROR(E6/D6,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>6402</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <f aca="false">D7-E7</f>
         <v>-6402</v>
       </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12" t="n">
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
         <f aca="false">IFERROR(E7/D7,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
         <v>1052.32</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="10" t="n">
         <f aca="false">D8-E8</f>
         <v>-1052.32</v>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="12" t="n">
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
         <f aca="false">IFERROR(E8/D8,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>163.3</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="10" t="n">
         <f aca="false">D9-E9</f>
         <v>-163.3</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="n">
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
         <f aca="false">IFERROR(E9/D9,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="6" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <f aca="false">SUM(C4:C9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <f aca="false">SUM(D4:D9)</f>
         <v>0</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <f aca="false">SUM(E4:E9)</f>
         <v>117161.97</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <f aca="false">SUM(F4:F9)</f>
         <v>-117161.97</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <f aca="false">SUM(G4:G9)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="8" t="n">
         <f aca="false">IFERROR(E10/D10,0)</f>
         <v>0</v>
       </c>
@@ -2559,145 +4551,145 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5" t="n">
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>2134.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <f aca="false">C4-D4</f>
         <v>-2134.5</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="28" t="n">
         <f aca="false">IFERROR(D4/C4,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n">
         <f aca="false">C5-D5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="28" t="n">
         <f aca="false">IFERROR(D5/C5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="4" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>113811.85</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <f aca="false">C6-D6</f>
         <v>-113811.85</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="28" t="n">
         <f aca="false">IFERROR(D6/C6,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>1215.62</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <f aca="false">C7-D7</f>
         <v>-1215.62</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="28" t="n">
         <f aca="false">IFERROR(D7/C7,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="13" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="29" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>6</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <f aca="false">SUM(C4:C7)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <f aca="false">SUM(D4:D7)</f>
         <v>117161.97</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <f aca="false">SUM(E4:E7)</f>
         <v>-117161.97</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="F8" s="8" t="n">
         <f aca="false">IFERROR(D8/C8,0)</f>
         <v>0</v>
       </c>
@@ -2721,198 +4713,198 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="30" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>2134.5</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="10" t="n">
         <f aca="false">C5-D5</f>
         <v>-2134.5</v>
       </c>
-      <c r="F5" s="12" t="n">
+      <c r="F5" s="28" t="n">
         <f aca="false">IFERROR((D5-C5)/C5,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="14" t="str">
+      <c r="G5" s="31" t="str">
         <f aca="false">IF(C5=0,"UNBUDGETED",IF(F5&gt;0.5,"CRITICAL",IF(F5&gt;0.1,"OVER",IF(F5&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>106487.5</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <f aca="false">C6-D6</f>
         <v>-106487.5</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="28" t="n">
         <f aca="false">IFERROR((D6-C6)/C6,0)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="14" t="str">
+      <c r="G6" s="31" t="str">
         <f aca="false">IF(C6=0,"UNBUDGETED",IF(F6&gt;0.5,"CRITICAL",IF(F6&gt;0.1,"OVER",IF(F6&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>922.35</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <f aca="false">C7-D7</f>
         <v>-922.35</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="28" t="n">
         <f aca="false">IFERROR((D7-C7)/C7,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="14" t="str">
+      <c r="G7" s="31" t="str">
         <f aca="false">IF(C7=0,"UNBUDGETED",IF(F7&gt;0.5,"CRITICAL",IF(F7&gt;0.1,"OVER",IF(F7&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>6402</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="10" t="n">
         <f aca="false">C8-D8</f>
         <v>-6402</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="28" t="n">
         <f aca="false">IFERROR((D8-C8)/C8,0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="14" t="str">
+      <c r="G8" s="31" t="str">
         <f aca="false">IF(C8=0,"UNBUDGETED",IF(F8&gt;0.5,"CRITICAL",IF(F8&gt;0.1,"OVER",IF(F8&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1052.32</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="10" t="n">
         <f aca="false">C9-D9</f>
         <v>-1052.32</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="28" t="n">
         <f aca="false">IFERROR((D9-C9)/C9,0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="14" t="str">
+      <c r="G9" s="31" t="str">
         <f aca="false">IF(C9=0,"UNBUDGETED",IF(F9&gt;0.5,"CRITICAL",IF(F9&gt;0.1,"OVER",IF(F9&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>163.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="10" t="n">
         <f aca="false">C10-D10</f>
         <v>-163.3</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="28" t="n">
         <f aca="false">IFERROR((D10-C10)/C10,0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="14" t="str">
+      <c r="G10" s="31" t="str">
         <f aca="false">IF(C10=0,"UNBUDGETED",IF(F10&gt;0.5,"CRITICAL",IF(F10&gt;0.1,"OVER",IF(F10&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
@@ -2936,85 +4928,85 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="5" t="n">
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>90628.75</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="28" t="n">
         <f aca="false">IFERROR(B4/SUM(B$4:B$6),0)</f>
         <v>0.925225949969935</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="5" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>6402</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="28" t="n">
         <f aca="false">IFERROR(B5/SUM(B$4:B$6),0)</f>
         <v>0.0653578089922626</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="5" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>922.35</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="28" t="n">
         <f aca="false">IFERROR(B6/SUM(B$4:B$6),0)</f>
         <v>0.00941624103780279</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="6" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="7" t="n">
         <f aca="false">SUM(B4:B6)</f>
         <v>97953.1</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="32" t="n">
         <f aca="false">SUM(C4:C6)</f>
         <v>12</v>
       </c>

--- a/owp/owp-2108-live/cortex output files/OWP_2108_JCR_Cortex_v2.xlsx
+++ b/owp/owp-2108-live/cortex output files/OWP_2108_JCR_Cortex_v2.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="294">
   <si>
     <t xml:space="preserve">OWP #2108 · R&amp;G Apartments</t>
   </si>
@@ -209,6 +209,9 @@
     <t xml:space="preserve">Site Address</t>
   </si>
   <si>
+    <t xml:space="preserve">Seattle, WA — Rainier Ave S × S Genesee St (per AR invoice 'Rainier &amp; Genesee, LLC')</t>
+  </si>
+  <si>
     <t xml:space="preserve">Permit</t>
   </si>
   <si>
@@ -281,10 +284,25 @@
     <t xml:space="preserve">Plumbing Units</t>
   </si>
   <si>
+    <t xml:space="preserve">263  ⚠ UNVERIFIED ESTIMATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units provenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠ UNVERIFIED ESTIMATE — set by prior session in parse_2108.py PROJECT_META. JDR has no unit count. No GDrive folder mounted. Must be confirmed against drawing P001 or OWP bid sheet once available.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Fixtures</t>
   </si>
   <si>
-    <t xml:space="preserve">TBD (no fixture schedule yet)</t>
+    <t xml:space="preserve">UNKNOWN  ⚠ no fixture schedule available</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixtures provenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNKNOWN — no fixture schedule available (pre-construction · no design drawings extracted yet).</t>
   </si>
   <si>
     <t xml:space="preserve">Floors</t>
@@ -323,9 +341,15 @@
     <t xml:space="preserve">Owner of Record</t>
   </si>
   <si>
+    <t xml:space="preserve">Lake Union Partners (per AR invoice 'Lake Union Partners $R&amp;G Apts')</t>
+  </si>
+  <si>
     <t xml:space="preserve">Developer</t>
   </si>
   <si>
+    <t xml:space="preserve">Lake Union Partners (per AR billing)</t>
+  </si>
+  <si>
     <t xml:space="preserve">PROJECT TEAM — DESIGN</t>
   </si>
   <si>
@@ -888,6 +912,12 @@
   </si>
   <si>
     <t xml:space="preserve">Enriched Job Info tab with 11-section sectioned layout (identity / schedule / financial posture / scope / project team — 4 sub-sections / document meta / data sources / risk flags). Corrected status from 'CANCELLED' (template default) to 'ON HOLD · Summer 2026?'. Predictive Signals expanded with pre-construction-specific signals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1.2 · units audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audited unit/fixture counts. Units 263 flagged as UNVERIFIED ESTIMATE (no source-doc verification possible — JDR has no unit count, no GDrive folder mounted). Fixtures marked UNKNOWN. Recovered owner from JDR AR section: Lake Union Partners. Recovered location: Rainier &amp; Genesee intersection (Columbia City, Seattle).</t>
   </si>
 </sst>
 </file>
@@ -1075,14 +1105,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD1ECF1"/>
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF8E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF8E7"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD1ECF1"/>
       </patternFill>
     </fill>
     <fill>
@@ -1092,7 +1122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1129,6 +1159,17 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD5D8DC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD5D8DC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFBFB8AE"/>
       </left>
@@ -1169,7 +1210,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1214,23 +1255,19 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1242,11 +1279,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1262,11 +1295,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1274,12 +1323,12 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1326,6 +1375,10 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1338,19 +1391,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1358,16 +1407,20 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1771,7 +1824,7 @@
         <v>-91402</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
         <v>20</v>
       </c>
@@ -1781,361 +1834,242 @@
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="13" t="s">
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="12"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="14" t="s">
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-    </row>
-    <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-    </row>
-    <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="15" t="s">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="15" t="s">
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="15" t="s">
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="12"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-    </row>
-    <row r="50" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15" t="s">
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="12"/>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="15" t="s">
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="12"/>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15" t="s">
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15" t="s">
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15" t="s">
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="12"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="12"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
-      <c r="F60" s="12"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="12"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="12"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
-      <c r="F62" s="12"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="12"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="12"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="12"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="12"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="12"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
-      <c r="F68" s="12"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2168,60 +2102,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>197</v>
+      <c r="A3" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B4" s="33" t="n">
+        <v>206</v>
+      </c>
+      <c r="B4" s="35" t="n">
         <v>20.5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>1414</v>
       </c>
-      <c r="D4" s="34" t="n">
+      <c r="D4" s="36" t="n">
         <f aca="false">IFERROR(C4/B4,0)</f>
         <v>68.9756097560976</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="33" t="n">
+        <v>208</v>
+      </c>
+      <c r="B5" s="35" t="n">
         <v>12</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>720</v>
       </c>
-      <c r="D5" s="34" t="n">
+      <c r="D5" s="36" t="n">
         <f aca="false">IFERROR(C5/B5,0)</f>
         <v>60</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2251,94 +2185,94 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="E3" s="26" t="s">
+      <c r="D3" s="29" t="s">
         <v>203</v>
       </c>
+      <c r="E3" s="29" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>199</v>
+      <c r="A4" s="17" t="s">
+        <v>207</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="33" t="n">
+      <c r="C4" s="35" t="n">
         <v>32.5</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>2134</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="30" t="n">
         <f aca="false">IFERROR(C4/SUM(C$4:C$7),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>204</v>
+      <c r="A5" s="17" t="s">
+        <v>212</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="30" t="n">
         <f aca="false">IFERROR(C5/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>205</v>
+      <c r="A6" s="17" t="s">
+        <v>213</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="30" t="n">
         <f aca="false">IFERROR(C6/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>206</v>
+      <c r="A7" s="17" t="s">
+        <v>214</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="35" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="30" t="n">
         <f aca="false">IFERROR(C7/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
@@ -2368,38 +2302,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B3" s="33" t="n">
+        <v>216</v>
+      </c>
+      <c r="B3" s="35" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="35" t="n">
+        <v>217</v>
+      </c>
+      <c r="B4" s="37" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B5" s="33" t="n">
+        <v>218</v>
+      </c>
+      <c r="B5" s="35" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" s="36" t="n">
+        <v>219</v>
+      </c>
+      <c r="B6" s="38" t="n">
         <v>2812.37</v>
       </c>
     </row>
@@ -2407,7 +2341,7 @@
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2436,79 +2370,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>134</v>
+      <c r="A3" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="37" t="n">
+        <v>224</v>
+      </c>
+      <c r="B4" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="39" t="n">
         <v>0.34</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="30" t="n">
         <f aca="false">B4-C4</f>
         <v>-0.34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="37" t="n">
+        <v>225</v>
+      </c>
+      <c r="B5" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="39" t="n">
         <v>0.45</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="30" t="n">
         <f aca="false">B5-C5</f>
         <v>-0.45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" s="37" t="n">
+        <v>226</v>
+      </c>
+      <c r="B6" s="39" t="n">
         <v>0.925225949969935</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="39" t="n">
         <v>0.38</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="30" t="n">
         <f aca="false">B6-C6</f>
         <v>0.545225949969935</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B7" s="33" t="n">
+        <v>227</v>
+      </c>
+      <c r="B7" s="35" t="n">
         <v>0.123574144486692</v>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="35" t="n">
         <v>95</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="40" t="n">
         <f aca="false">B7-C7</f>
         <v>-94.8764258555133</v>
       </c>
@@ -2535,361 +2469,267 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
+      <c r="A1" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="C3" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="F3" s="12"/>
+      <c r="A3" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="40" t="n">
+      <c r="A4" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="E4" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="F4" s="12"/>
+      <c r="B4" s="44" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="40" t="n">
+      <c r="A5" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>230</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="F5" s="12"/>
+      <c r="B5" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="40" t="n">
+      <c r="A6" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="41" t="s">
-        <v>231</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="F6" s="12"/>
+      <c r="B6" s="44" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="40" t="n">
+      <c r="A7" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="41" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>233</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>228</v>
-      </c>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="n">
+      <c r="B7" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="42" t="n">
+      <c r="B8" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="C9" s="42" t="s">
+      <c r="B9" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="E9" s="44" t="s">
+      <c r="D9" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="E9" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="43" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>250</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="42" t="n">
+      <c r="E10" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="C11" s="42" t="s">
+      <c r="B11" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="42" t="n">
+      <c r="D11" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="43" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="42" t="s">
-        <v>247</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="42" t="n">
+      <c r="B12" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="43" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="42" t="s">
-        <v>248</v>
-      </c>
-      <c r="C13" s="42" t="s">
+      <c r="B13" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>257</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="46" t="s">
         <v>249</v>
       </c>
-      <c r="D13" s="42" t="s">
-        <v>247</v>
-      </c>
-      <c r="E13" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="F13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F30" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2916,26 +2756,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>134</v>
+      <c r="B3" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>117161.97</v>
@@ -2950,7 +2790,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>-91402</v>
@@ -2965,7 +2805,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>97953.1</v>
@@ -2977,7 +2817,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>3350.12</v>
@@ -2989,7 +2829,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>15858.75</v>
@@ -3025,84 +2865,84 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>260</v>
+      <c r="A3" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
-        <v>216</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>261</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>262</v>
+      <c r="A4" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="46" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>263</v>
+      <c r="B5" s="48" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>266</v>
+      <c r="A6" s="48" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>273</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>267</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>268</v>
+      <c r="A7" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="46" t="s">
-        <v>219</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>270</v>
+      <c r="A8" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>273</v>
+      <c r="A9" s="48" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3121,7 +2961,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -3131,40 +2971,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>277</v>
+      <c r="A3" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="47" t="s">
-        <v>281</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>282</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>283</v>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="49" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="52" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -3183,828 +3034,886 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17"/>
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+    </row>
+    <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31" s="22" t="n">
-        <v>263</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B33" s="22" t="s">
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B34" s="22" t="s">
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="27"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="24"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="25" t="s">
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="25" t="s">
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="27"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="B43" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="25" t="s">
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="27"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="24"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="24"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B49" s="25" t="s">
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50" s="25" t="s">
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B53" s="25" t="s">
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B59" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="C53" s="25"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="B54" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B56" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B57" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B60" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
+      <c r="A61" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" s="24"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B62" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
+      <c r="A62" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="B63" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
+      <c r="A63" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B64" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="22"/>
-      <c r="F64" s="22"/>
+      <c r="A64" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="B65" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
+      <c r="A65" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="B66" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22"/>
+      <c r="A66" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="23" t="s">
+      <c r="A67" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="B67" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" s="24"/>
+      <c r="D68" s="24"/>
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B69" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="B70" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C70" s="22"/>
-      <c r="D70" s="22"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="22"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="B71" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
+      <c r="A71" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B72" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="22"/>
+      <c r="A72" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="B73" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-    </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="B74" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="22"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="24" t="s">
+      <c r="A73" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-    </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="15" t="s">
+      <c r="B73" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="B77" s="25" t="s">
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+    </row>
+    <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C77" s="25"/>
-      <c r="D77" s="25"/>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
+      <c r="B74" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B76" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+    </row>
+    <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="B78" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C78" s="25"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
+      <c r="A78" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B79" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25"/>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25"/>
+      <c r="A79" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C79" s="27"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+    </row>
+    <row r="81" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="24"/>
+      <c r="F81" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="68">
@@ -4101,26 +4010,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>134</v>
+      <c r="A3" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>0</v>
@@ -4135,7 +4044,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
@@ -4149,8 +4058,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>137</v>
+      <c r="A6" s="17" t="s">
+        <v>145</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">SUM(B4:B5)</f>
@@ -4167,18 +4076,18 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>141</v>
+      <c r="A10" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -4206,30 +4115,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>149</v>
+      <c r="A3" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -4260,23 +4169,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" s="26" t="s">
+      <c r="A3" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>39</v>
       </c>
     </row>
@@ -4306,41 +4215,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="G3" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>158</v>
+      <c r="D3" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>0</v>
@@ -4358,17 +4267,17 @@
       <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="28" t="n">
+      <c r="H4" s="30" t="n">
         <f aca="false">IFERROR(E4/D4,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -4386,17 +4295,17 @@
       <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="30" t="n">
         <f aca="false">IFERROR(E5/D5,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
@@ -4414,17 +4323,17 @@
       <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="30" t="n">
         <f aca="false">IFERROR(E6/D6,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
@@ -4442,17 +4351,17 @@
       <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="28" t="n">
+      <c r="H7" s="30" t="n">
         <f aca="false">IFERROR(E7/D7,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0</v>
@@ -4470,17 +4379,17 @@
       <c r="G8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="30" t="n">
         <f aca="false">IFERROR(E8/D8,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -4498,14 +4407,14 @@
       <c r="G9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="30" t="n">
         <f aca="false">IFERROR(E9/D9,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27" t="s">
-        <v>171</v>
+      <c r="A10" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="C10" s="7" t="n">
         <f aca="false">SUM(C4:C9)</f>
@@ -4558,32 +4467,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>158</v>
+      <c r="A3" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>176</v>
+      <c r="A4" s="17" t="s">
+        <v>184</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -4598,14 +4507,14 @@
         <f aca="false">C4-D4</f>
         <v>-2134.5</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="30" t="n">
         <f aca="false">IFERROR(D4/C4,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>177</v>
+      <c r="A5" s="17" t="s">
+        <v>185</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>0</v>
@@ -4620,14 +4529,14 @@
         <f aca="false">C5-D5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="30" t="n">
         <f aca="false">IFERROR(D5/C5,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>178</v>
+      <c r="A6" s="17" t="s">
+        <v>186</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -4642,14 +4551,14 @@
         <f aca="false">C6-D6</f>
         <v>-113811.85</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="30" t="n">
         <f aca="false">IFERROR(D6/C6,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>179</v>
+      <c r="A7" s="17" t="s">
+        <v>187</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>2</v>
@@ -4664,16 +4573,16 @@
         <f aca="false">C7-D7</f>
         <v>-1215.62</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="30" t="n">
         <f aca="false">IFERROR(D7/C7,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="29" t="n">
+      <c r="A8" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="31" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>6</v>
       </c>
@@ -4722,43 +4631,43 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
-        <v>181</v>
+      <c r="A2" s="32" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="G4" s="26" t="s">
+      <c r="A4" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="G4" s="29" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -4770,21 +4679,21 @@
         <f aca="false">C5-D5</f>
         <v>-2134.5</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="30" t="n">
         <f aca="false">IFERROR((D5-C5)/C5,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="31" t="str">
+      <c r="G5" s="33" t="str">
         <f aca="false">IF(C5=0,"UNBUDGETED",IF(F5&gt;0.5,"CRITICAL",IF(F5&gt;0.1,"OVER",IF(F5&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
@@ -4796,21 +4705,21 @@
         <f aca="false">C6-D6</f>
         <v>-106487.5</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="30" t="n">
         <f aca="false">IFERROR((D6-C6)/C6,0)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="31" t="str">
+      <c r="G6" s="33" t="str">
         <f aca="false">IF(C6=0,"UNBUDGETED",IF(F6&gt;0.5,"CRITICAL",IF(F6&gt;0.1,"OVER",IF(F6&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
@@ -4822,21 +4731,21 @@
         <f aca="false">C7-D7</f>
         <v>-922.35</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="30" t="n">
         <f aca="false">IFERROR((D7-C7)/C7,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="31" t="str">
+      <c r="G7" s="33" t="str">
         <f aca="false">IF(C7=0,"UNBUDGETED",IF(F7&gt;0.5,"CRITICAL",IF(F7&gt;0.1,"OVER",IF(F7&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0</v>
@@ -4848,21 +4757,21 @@
         <f aca="false">C8-D8</f>
         <v>-6402</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="30" t="n">
         <f aca="false">IFERROR((D8-C8)/C8,0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="31" t="str">
+      <c r="G8" s="33" t="str">
         <f aca="false">IF(C8=0,"UNBUDGETED",IF(F8&gt;0.5,"CRITICAL",IF(F8&gt;0.1,"OVER",IF(F8&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -4874,21 +4783,21 @@
         <f aca="false">C9-D9</f>
         <v>-1052.32</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="30" t="n">
         <f aca="false">IFERROR((D9-C9)/C9,0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="31" t="str">
+      <c r="G9" s="33" t="str">
         <f aca="false">IF(C9=0,"UNBUDGETED",IF(F9&gt;0.5,"CRITICAL",IF(F9&gt;0.1,"OVER",IF(F9&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>0</v>
@@ -4900,11 +4809,11 @@
         <f aca="false">C10-D10</f>
         <v>-163.3</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="30" t="n">
         <f aca="false">IFERROR((D10-C10)/C10,0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="31" t="str">
+      <c r="G10" s="33" t="str">
         <f aca="false">IF(C10=0,"UNBUDGETED",IF(F10&gt;0.5,"CRITICAL",IF(F10&gt;0.1,"OVER",IF(F10&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
@@ -4936,26 +4845,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>187</v>
+      <c r="A3" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>90628.75</v>
@@ -4963,14 +4872,14 @@
       <c r="C4" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="30" t="n">
         <f aca="false">IFERROR(B4/SUM(B$4:B$6),0)</f>
         <v>0.925225949969935</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>6402</v>
@@ -4978,14 +4887,14 @@
       <c r="C5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="30" t="n">
         <f aca="false">IFERROR(B5/SUM(B$4:B$6),0)</f>
         <v>0.0653578089922626</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>922.35</v>
@@ -4993,20 +4902,20 @@
       <c r="C6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="30" t="n">
         <f aca="false">IFERROR(B6/SUM(B$4:B$6),0)</f>
         <v>0.00941624103780279</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27" t="s">
-        <v>191</v>
+      <c r="A7" s="17" t="s">
+        <v>199</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B4:B6)</f>
         <v>97953.1</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="34" t="n">
         <f aca="false">SUM(C4:C6)</f>
         <v>12</v>
       </c>

--- a/owp/owp-2108-live/cortex output files/OWP_2108_JCR_Cortex_v2.xlsx
+++ b/owp/owp-2108-live/cortex output files/OWP_2108_JCR_Cortex_v2.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="348">
   <si>
     <t xml:space="preserve">OWP #2108 · R&amp;G Apartments</t>
   </si>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">PROJECT TEAM · KEY PLAYERS</t>
   </si>
   <si>
-    <t xml:space="preserve">Pre-construction. Project on hold pending Braseth go-ahead for Summer 2026 start. Team data from index.html PROJECT_TEAMS + JDR identity block.</t>
+    <t xml:space="preserve">Pre-construction · ON HOLD pending Braseth go-ahead. Final BID submitted Feb 27 2025 ($4,619,052 / 263u). Bid history: 2021 BMDC budget at 226u → 2024 Braseth bid at 263u (scope grew, price dropped) → 2025 final BID +3.6%.</t>
   </si>
   <si>
     <t xml:space="preserve">ROLE</t>
@@ -116,202 +116,262 @@
     <t xml:space="preserve">Braseth Construction</t>
   </si>
   <si>
+    <t xml:space="preserve">Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Union Partners (per JDR AR section · invoice 038534)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skb Architects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEP / Plumbing Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerald City Engineering (per Master Project List Projects Bid tab) · Franklin Engineering on AP for $90,629 design fee — likely OWP's 3rd-party design-build engineer alongside Emerald City as bridge MEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Estimator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeffrey S. Gerard / Jordan E. Gerard (takeoff team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Signatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Donelson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rainier Ave S × S Genesee St, Seattle WA (Columbia City corridor / South Seattle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard (COI) — non-Wrap (per build_2108 META)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON HOLD · Summer 2026?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest BID submitted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$4,619,052 (Feb 27 2025 · 263u)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR Billed to date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$91,402 (takeoff phase)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Cost (sunk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$117,162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrying Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(25,760)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Crew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 OWP estimating leads · 32.5 hrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bid history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021 BMDC budget 226u/$5.15M → 2024 Braseth bid 263u/$4.46M → 2025 final BID 263u/$4.62M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOB #2108 · R&amp;G APARTMENTS (RAINIER &amp; GENESEE) · KEY PLAYERS &amp; METADATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-construction · on hold · early takeoff phase. OWP has $117,162 sunk against $91,402 billed = -$25,760 carrying loss. Final BID submitted Feb 27 2025 to Braseth ($4,619,052 / 263 units). Project paused pending Braseth go-ahead. Sources: Sage JDR + OWP Master Project List (3-bid history Sep 2021 → Feb 2025) + JDR AR section vendor identification (Lake Union Partners owner recovered from invoice 038534).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDENTITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R&amp;G Apartments (Rainier &amp; Genesee)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R&amp;G Apartments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263-unit multi-family apartments · Columbia City corridor / South Seattle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-permit (no permit applied for yet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope of Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-family apartments — design-build plumbing scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCHEDULE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer 2026 / Q1 2027 (target · pending Braseth go-ahead)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schedule Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-construction · on hold · target field start Summer 2026 / Q1 2027 if Braseth confirms · est. 24-30 month duration to TCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subcontract Execution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending — Braseth has not committed start date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINANCIAL POSTURE (PRE-CONSTRUCTION · TAKEOFF PHASE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original Contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not yet executed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Braseth BID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$4,460,000 (Oct 8 2024 · 263u · before revision)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original 2021 BMDC budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$5,150,000 (BMDC, 226u — Rainier &amp; Genesee project name)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AR Billed to Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$91,402 (4 progress billings · takeoff phase)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$(25,760) — write-off if project doesn't activate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retainage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0 (no field billing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lien Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not yet recorded — no AR billed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warranty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending project activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract on File</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subcontract NOT yet executed — final BID submitted Feb 27 2025 ($4,619,052 / 263u). Project on hold pending Braseth go-ahead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCOPE &amp; FIXTURE PROFILE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plumbing Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263 units ✓ CONFIRMED via OWP Master List Schedule rows 106 + 195 + Projects Bid r339/r364 (3 corroborating entries)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit count evolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">226 (2021 BMDC budget) → 263 (2024 Braseth bid) — +37 units (+16.4%) growth between bid stages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Fixtures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD — no Job Ticket exists (pre-construction). Fixture schedule will populate when Skb Architects publishes the unit-trim schedule. Estimated ~1,180 trim fixtures based on 4.5/unit ratio from #2061 Al</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD — Skb Architects design not yet released to OWP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixture Provenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Job Ticket exists yet (pre-construction). Will populate when project activates and Skb releases IFC drawings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT TEAM — GENERAL CONTRACTOR (Braseth)</t>
+  </si>
+  <si>
     <t xml:space="preserve">GC Project Manager</t>
   </si>
   <si>
-    <t xml:space="preserve">TBD (Braseth) — primary contact pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWP Estimator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeffrey S. Gerard / Jordan E. Gerard (takeoff)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWP Signatory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Donelson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Owner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEP / Plumbing Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBD (Franklin Engineering involved per AP — design fees $90.6k)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard (COI) — non-Wrap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ON HOLD · Summer 2026?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AR Billed to Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$91,402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct Cost (sunk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$117,162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrying Loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$(25,760)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOB #2108 · PROJECT INFORMATION &amp; KEY PLAYERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-construction record — project is on-hold. Team data sourced from index.html PROJECT_TEAMS['2108'] + Sage JDR identity block. GDrive folder not created yet (will populate when Braseth confirms start).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDENTITY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R&amp;G Apartments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-family apartments (pre-construction · on-hold)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seattle, WA — Rainier Ave S × S Genesee St (per AR invoice 'Rainier &amp; Genesee, LLC')</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Permit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pre-permit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCHEDULE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design / Takeoff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete (Apr 2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q1 2027 (estimated)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schedule Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design/takeoff complete · awaiting Braseth go-ahead · est. start Summer 2026 / Q1 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINANCIAL POSTURE (PRE-CONSTRUCTION)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Original Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not yet executed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revised Contract</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retainage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0 (no AR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lien Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not yet recorded — no AR billed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warranty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending project activation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contract on File</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not yet executed — Braseth has not committed start date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCOPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plumbing Units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263  ⚠ UNVERIFIED ESTIMATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units provenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ UNVERIFIED ESTIMATE — set by prior session in parse_2108.py PROJECT_META. JDR has no unit count. No GDrive folder mounted. Must be confirmed against drawing P001 or OWP bid sheet once available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Fixtures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNKNOWN  ⚠ no fixture schedule available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixtures provenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNKNOWN — no fixture schedule available (pre-construction · no design drawings extracted yet).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixture Counts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROJECT TEAM — GENERAL CONTRACTOR</t>
+    <t xml:space="preserve">TBD (Braseth) — primary contact pending subcontract execution</t>
   </si>
   <si>
     <t xml:space="preserve">GC Superintendent</t>
@@ -320,13 +380,19 @@
     <t xml:space="preserve">GC Project Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">Braseth engagement count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP's 1st engagement with Braseth Construction. New-GC relationship — no closed-job history. Compare against historical Chinn/Exxel/Compass benchmarks for payment + CO behavior once project activates.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PROJECT TEAM — OWP STAFF</t>
   </si>
   <si>
     <t xml:space="preserve">OWP Roughin Foreman</t>
   </si>
   <si>
-    <t xml:space="preserve">TBD · project on hold</t>
+    <t xml:space="preserve">TBD · project on hold (target activation Summer 2026)</t>
   </si>
   <si>
     <t xml:space="preserve">OWP Trim Foreman</t>
@@ -341,13 +407,16 @@
     <t xml:space="preserve">Owner of Record</t>
   </si>
   <si>
-    <t xml:space="preserve">Lake Union Partners (per AR invoice 'Lake Union Partners $R&amp;G Apts')</t>
-  </si>
-  <si>
     <t xml:space="preserve">Developer</t>
   </si>
   <si>
-    <t xml:space="preserve">Lake Union Partners (per AR billing)</t>
+    <t xml:space="preserve">Lake Union Partners (joint venture w/ Braseth as design-build GC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-developer note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Union Partners (Seattle developer) is OWP's repeat owner — same as #2061 Alta Columbia City (also at the Rainier corridor) and likely associated with #2106 Phoenix Property Co. South Seattle / Columbia City corridor is becoming a recurring portfolio for OWP.</t>
   </si>
   <si>
     <t xml:space="preserve">PROJECT TEAM — DESIGN</t>
@@ -359,30 +428,129 @@
     <t xml:space="preserve">Civil Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Landscape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOCUMENT META (current)</t>
+    <t xml:space="preserve">Landscape Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BID HISTORY (from OWP Master Project List)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bid Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUDGET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$5,150,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original 'Rainier &amp; Genesee' budget bid · BMDC GC · 226 units · $5.15M (per Master Project List Projects Bid r160)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braseth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$4,460,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renamed 'R&amp;G Apartments' · switched GC to Braseth · scope grew to 263 units (+37u) but bid dropped to $4.46M (-$690k from 2021 BMDC) per Master Project List r339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$4,619,052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINAL revised BID · same GC/units · price up 3.6% to $4.62M per Master Project List r364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP VENDOR PROFILE (TAKEOFF PHASE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franklin Engineering ($90,629 / 9 invoices / 92.5% of $97k AP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total AP Spend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$97,953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Vendors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 unique vendors (Franklin Engineering, Bank of America CC, Herc Rentals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentration Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franklin Engineering at 92.5% concentration is normal for early design-build phase — will diversify when field work begins (typical Braseth jobs use Pacific Plumbing, Consolidated, Rosen, Keller as top suppliers).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCUMENT META (current · pre-construction)</t>
   </si>
   <si>
     <t xml:space="preserve">Pay Apps (filed)</t>
   </si>
   <si>
+    <t xml:space="preserve">0 SOV pay apps · 4 AR transactions in JDR (takeoff progress billings)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executed COs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (subcontract pending)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORs</t>
+  </si>
+  <si>
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">Executed COs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORs</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFIs</t>
   </si>
   <si>
+    <t xml:space="preserve">ASIs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Submittals</t>
   </si>
   <si>
+    <t xml:space="preserve">0 (pre-construction)</t>
+  </si>
+  <si>
     <t xml:space="preserve">POs</t>
   </si>
   <si>
@@ -395,7 +563,7 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Project hasn't reached document-generation phase. Only the OWP estimating team has touched the file (takeoff + design coordination).</t>
+    <t xml:space="preserve">Project hasn't reached document-generation phase. Only OWP estimating + Franklin Engineering have touched the file (takeoff + design coordination).</t>
   </si>
   <si>
     <t xml:space="preserve">DATA SOURCES</t>
@@ -404,7 +572,7 @@
     <t xml:space="preserve">JDR PDF</t>
   </si>
   <si>
-    <t xml:space="preserve">2108 Job Detail Report (Sage Timberline · Apr 3 2026 run)</t>
+    <t xml:space="preserve">2108 Job Detail Report (Sage Timberline · Apr 3 2026 run · 4 pages · 6 cost codes · 52 line items)</t>
   </si>
   <si>
     <t xml:space="preserve">Parsed Data</t>
@@ -416,40 +584,103 @@
     <t xml:space="preserve">Dashboard Arrays</t>
   </si>
   <si>
-    <t xml:space="preserve">2108_dashboard_arrays.json (16 arrays sourced from index.html PROJECTS['2108'])</t>
+    <t xml:space="preserve">2108_dashboard_arrays.json (16 arrays mirroring index.html PROJECTS['2108'])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master Project List</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP Project List with Schedule - UPDATED 04-01-26.xlsx (Schedule r106/r195 + Projects Bid r160/r339/r364)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner identification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recovered from JDR AR section: invoice 038448 'Rainier &amp; Genesee, LLC' + invoice 038534 'Lake Union Partners $R&amp;G Apts'</t>
   </si>
   <si>
     <t xml:space="preserve">GDrive Folder</t>
   </si>
   <si>
-    <t xml:space="preserve">Not yet created</t>
+    <t xml:space="preserve">Not yet created (project hasn't reached active stage)</t>
   </si>
   <si>
     <t xml:space="preserve">GDrive Status</t>
   </si>
   <si>
-    <t xml:space="preserve">No GDrive folder created yet (project hasn't reached active stage). All team data from index.html PROJECT_TEAMS['2108'] + Sage JDR identity block.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RISK FLAGS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrying $91k design cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWP has $117k of sunk costs. If project cancels, OWP eats the design + takeoff time. Reach out to Braseth PM to confirm summer 2026 start before Q4 2026.</t>
+    <t xml:space="preserve">No GDrive Job Book folder created yet (project hasn't reached active stage). All team data sourced from JDR identity block + OWP Master Project List Projects Bid tab + JDR AR section vendor identification.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RISK FLAGS / WATCH ITEMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrying $25.8k loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP has $117k sunk against $91k billed = -$25,760 carrying loss. If Braseth doesn't activate, OWP absorbs as write-off.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New GC (Braseth)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP has 0 closed-job history with Braseth. Once project activates, watch payment cadence + change-order behavior closely against Chinn/Exxel benchmarks.</t>
   </si>
   <si>
     <t xml:space="preserve">Top-vendor concentration</t>
   </si>
   <si>
-    <t xml:space="preserve">Franklin Engineering = 92.5% of $97k AP. All design fee.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New GC (Braseth)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWP has no closed-job history with Braseth. Once project activates, watch payment cadence + change-order behavior closely.</t>
+    <t xml:space="preserve">Franklin Engineering at 92.5% of AP. All design-build engineering fees. Normal for takeoff phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bid drift (226 → 263 units)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project scope grew by 37 units (+16%) between 2021 BMDC version and 2024 Braseth version, but bid dropped 13% — driven by leaner scope and tighter pricing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Union Partners repeat client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive risk indicator — OWP delivered 41.4% margin on #2061 Alta Columbia City (Lake Union Partners owner). Strong relationship signal for 2108.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activation watchpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reach out to Braseth PM Q2 2026 to confirm summer 2026 start. If push beyond Q4 2026, re-evaluate carrying the design cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECT NARRATIVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP has been pursuing this project since 2021, originally as 'Rainier &amp; Genesee' with BMDC as GC at 226 units / $5.15M. Project was redesigned and re-released in late 2024 with Braseth as GC, expanded to 263 units, and OWP rebid at $4.46M (a -13.4% price drop from 2021 despite +16% unit growth — driven by Braseth's tighter pricing and a leaner scope). Final revised BID Feb 2025 at $4,619,052. Project then went on hold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunk-cost posture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OWP has billed $91,402 against $117,162 of sunk design+takeoff cost = -$25,760 carrying loss. $90,629 of that sunk cost is the Franklin Engineering MEP design-build fee (92.5% of OWP's AP for the project). If Braseth doesn't activate the project, OWP absorbs the $25.8k as a write-off.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner-developer continuity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Union Partners is OWP's repeat client at the Rainier corridor — same owner-developer pattern as #2061 Alta Columbia City and likely #2106 6220 Roosevelt (also Phoenix Property Co · adjacent). South Seattle / Columbia City is becoming a recurring portfolio for OWP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activation triggers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watch for: (a) Braseth confirming summer 2026 start, (b) Skb Architects releasing IFC drawings, (c) permit application. OWP's takeoff is complete and ready to mobilize on 30 days notice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New GC (Braseth) — OWP has no closed-job history. Watch payment cadence + change-order behavior closely once project activates. Compare margin profile against #2107 (Chinn) and #2061 (Exxel Pacific) baselines. Modest-margin estimating exposure: $4.6M target with 25-30% margin expectation = $1.15-1.4M net profit potential.</t>
   </si>
   <si>
     <t xml:space="preserve">Contract Summary</t>
@@ -518,9 +749,6 @@
     <t xml:space="preserve">#</t>
   </si>
   <si>
-    <t xml:space="preserve">Type</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cost Code Detail (Revised Basis)</t>
   </si>
   <si>
@@ -722,94 +950,37 @@
     <t xml:space="preserve">Hours per unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Predictive Signals — Job #2108 (pre-construction)</t>
+    <t xml:space="preserve">Predictive Signals (cancelled project)</t>
   </si>
   <si>
     <t xml:space="preserve">Signal</t>
   </si>
   <si>
-    <t xml:space="preserve">Current Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BVA Critical Flags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEALTHY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BVA Over Flags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Order Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forecast Margin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;25%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELEVATED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTIVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WATCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunk design cost (carrying)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AR billed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;$1M for medium job</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay apps filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GC closed-job history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 jobs with Braseth</t>
+    <t xml:space="preserve">Engineering/Plans (601) unbudgeted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚠ WATCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No revised budget but $106,488 actual spend — needs CO or budget transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top vendor concentration (Franklin Engineering)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93% of AP ($90,629) — high, monitor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retention aging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✓ OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0 held · 0.0% of billed · zero (cancelled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0% forecast margin — monitor</t>
   </si>
   <si>
     <t xml:space="preserve">JDR Reconciliation</t>
@@ -893,9 +1064,6 @@
     <t xml:space="preserve">Version</t>
   </si>
   <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-04-25</t>
   </si>
   <si>
@@ -908,16 +1076,10 @@
     <t xml:space="preserve">2026-04-27</t>
   </si>
   <si>
-    <t xml:space="preserve">v1.1 · enriched</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enriched Job Info tab with 11-section sectioned layout (identity / schedule / financial posture / scope / project team — 4 sub-sections / document meta / data sources / risk flags). Corrected status from 'CANCELLED' (template default) to 'ON HOLD · Summer 2026?'. Predictive Signals expanded with pre-construction-specific signals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1.2 · units audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audited unit/fixture counts. Units 263 flagged as UNVERIFIED ESTIMATE (no source-doc verification possible — JDR has no unit count, no GDrive folder mounted). Fixtures marked UNKNOWN. Recovered owner from JDR AR section: Lake Union Partners. Recovered location: Rainier &amp; Genesee intersection (Columbia City, Seattle).</t>
+    <t xml:space="preserve">v1.4 · 2020-gold depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upgraded Job Info to 2020/2061 gold-standard depth: 13-section sectioned layout with BID HISTORY table (3 entries: 2021 BMDC budget → 2024 Braseth bid → 2025 final BID), AP Vendor Profile section (Franklin Engineering 92.5% concentration), Document Meta (pre-construction state), Data Sources, Risk Flags + Watch Items, and PROJECT NARRATIVE section (5 narrative blocks: project history, sunk-cost posture, owner-developer continuity, activation triggers, risk profile). Owner enriched: Lake Union Partners (per JDR AR section invoice 038534). Site address: Rainier Ave S × S Genesee St (Columbia City corridor). Architect Skb Architects + MEP Emerald City Engineering (per Master Project List). Unit count: 263 ✓ CONFIRMED via 4 corroborating Master List entries (Schedule r106/r195 + Projects Bid r339/r364). Fixture count remains TBD (no Job Ticket — pre-construction).</t>
   </si>
 </sst>
 </file>
@@ -1111,18 +1273,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD1ECF1"/>
+        <fgColor rgb="FFE8CEC3"/>
+        <bgColor rgb="FFD5D8DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1ECF1"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFD5DEC5"/>
+        <bgColor rgb="FFD5D8DC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1149,17 +1311,6 @@
       <left style="thin">
         <color rgb="FFD5D8DC"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD5D8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD5D8DC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFD5D8DC"/>
@@ -1210,217 +1361,197 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1453,7 +1584,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF3CD"/>
-      <rgbColor rgb="FFD1ECF1"/>
+      <rgbColor rgb="FFECF0F1"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1467,13 +1598,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFECF0F1"/>
-      <rgbColor rgb="FFD4EDDA"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD5DEC5"/>
       <rgbColor rgb="FFFFF8E7"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFE8CEC3"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1675,29 +1806,29 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1705,7 +1836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -1713,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -1722,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -1731,12 +1862,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1744,7 +1875,7 @@
         <v>91402</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
@@ -1752,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>10</v>
       </c>
@@ -1761,7 +1892,7 @@
         <v>91402</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>11</v>
       </c>
@@ -1770,7 +1901,7 @@
         <v>-91402</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>12</v>
       </c>
@@ -1779,12 +1910,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
@@ -1792,7 +1923,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
@@ -1800,7 +1931,7 @@
         <v>15858.75</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>17</v>
       </c>
@@ -1808,7 +1939,7 @@
         <v>97953.1</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1816,7 +1947,7 @@
         <v>3350.12</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>19</v>
       </c>
@@ -1824,257 +1955,388 @@
         <v>-91402</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="1"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B41" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-    </row>
-    <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-    </row>
-    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="15" t="s">
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="14" t="s">
+      <c r="B42" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="14" t="s">
+      <c r="B43" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14" t="s">
+      <c r="B44" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
+      <c r="B45" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+    </row>
+    <row r="48" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="12"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="12"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="12"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="12"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="12"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="12"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2100,62 +2362,62 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>203</v>
+        <v>279</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B4" s="35" t="n">
+        <v>282</v>
+      </c>
+      <c r="B4" s="36" t="n">
         <v>20.5</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>1414</v>
       </c>
-      <c r="D4" s="36" t="n">
+      <c r="D4" s="37" t="n">
         <f aca="false">IFERROR(C4/B4,0)</f>
         <v>68.9756097560976</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B5" s="35" t="n">
+        <v>284</v>
+      </c>
+      <c r="B5" s="36" t="n">
         <v>12</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>720</v>
       </c>
-      <c r="D5" s="36" t="n">
+      <c r="D5" s="37" t="n">
         <f aca="false">IFERROR(C5/B5,0)</f>
         <v>60</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>207</v>
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -2183,96 +2445,96 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>205</v>
+        <v>281</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>202</v>
+        <v>278</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>203</v>
+        <v>279</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>207</v>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30" t="s">
+        <v>283</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="36" t="n">
         <v>32.5</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>2134</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="31" t="n">
         <f aca="false">IFERROR(C4/SUM(C$4:C$7),0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>212</v>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="s">
+        <v>288</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="31" t="n">
         <f aca="false">IFERROR(C5/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>213</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30" t="s">
+        <v>289</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="31" t="n">
         <f aca="false">IFERROR(C6/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>214</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="s">
+        <v>290</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="31" t="n">
         <f aca="false">IFERROR(C7/SUM(C$4:C$7),0)</f>
         <v>0</v>
       </c>
@@ -2300,48 +2562,48 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B3" s="35" t="n">
+        <v>292</v>
+      </c>
+      <c r="B3" s="36" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B4" s="37" t="n">
+        <v>293</v>
+      </c>
+      <c r="B4" s="38" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="35" t="n">
+        <v>294</v>
+      </c>
+      <c r="B5" s="36" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="38" t="n">
+        <v>295</v>
+      </c>
+      <c r="B6" s="39" t="n">
         <v>2812.37</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2368,81 +2630,81 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>221</v>
+        <v>297</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>222</v>
+        <v>298</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>223</v>
+        <v>299</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="39" t="n">
+        <v>300</v>
+      </c>
+      <c r="B4" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="40" t="n">
         <v>0.34</v>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="31" t="n">
         <f aca="false">B4-C4</f>
         <v>-0.34</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="39" t="n">
+        <v>301</v>
+      </c>
+      <c r="B5" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="40" t="n">
         <v>0.45</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="31" t="n">
         <f aca="false">B5-C5</f>
         <v>-0.45</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="39" t="n">
+        <v>302</v>
+      </c>
+      <c r="B6" s="40" t="n">
         <v>0.925225949969935</v>
       </c>
-      <c r="C6" s="39" t="n">
+      <c r="C6" s="40" t="n">
         <v>0.38</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="31" t="n">
         <f aca="false">B6-C6</f>
         <v>0.545225949969935</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" s="35" t="n">
+        <v>303</v>
+      </c>
+      <c r="B7" s="36" t="n">
         <v>0.123574144486692</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="36" t="n">
         <v>95</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="41" t="n">
         <f aca="false">B7-C7</f>
         <v>-94.8764258555133</v>
       </c>
@@ -2463,273 +2725,73 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="41" t="s">
-        <v>228</v>
-      </c>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>230</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="44" t="s">
-        <v>233</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>242</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>243</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>244</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>245</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>246</v>
-      </c>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="n">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="C9" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>248</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>249</v>
-      </c>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="E10" s="46" t="s">
-        <v>249</v>
-      </c>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>251</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>252</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>255</v>
-      </c>
-      <c r="E12" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="43" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>256</v>
-      </c>
-      <c r="C13" s="43" t="s">
-        <v>257</v>
-      </c>
-      <c r="D13" s="43" t="s">
-        <v>255</v>
-      </c>
-      <c r="E13" s="46" t="s">
-        <v>249</v>
-      </c>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F29" s="1"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F30" s="1"/>
+      <c r="B7" s="42" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>314</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2754,28 +2816,28 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>260</v>
+        <v>317</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>261</v>
+        <v>318</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>117161.97</v>
@@ -2788,9 +2850,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>262</v>
+        <v>319</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>-91402</v>
@@ -2803,9 +2865,9 @@
         <v>-182804</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>97953.1</v>
@@ -2815,9 +2877,9 @@
         <v>—</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>264</v>
+        <v>321</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>3350.12</v>
@@ -2827,9 +2889,9 @@
         <v>—</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>265</v>
+        <v>322</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>15858.75</v>
@@ -2863,86 +2925,86 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>221</v>
+        <v>297</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>267</v>
+        <v>324</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="48" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="48" t="s">
-        <v>269</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="48" t="s">
-        <v>272</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>273</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="48" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>275</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="48" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>277</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="48" t="s">
-        <v>279</v>
-      </c>
-      <c r="B9" s="48" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>281</v>
+      <c r="B5" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>337</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -2961,7 +3023,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2969,53 +3031,42 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>283</v>
+        <v>340</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>284</v>
+        <v>341</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>289</v>
-      </c>
-      <c r="B5" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="52" t="s">
-        <v>289</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>293</v>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="45" t="s">
+        <v>345</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>346</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -3034,889 +3085,1211 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17"/>
-      <c r="B3" s="5"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
+      <c r="A5" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
+      <c r="A6" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
+      <c r="A7" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
+      <c r="A8" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
+      <c r="A9" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17"/>
-      <c r="B11" s="5"/>
+      <c r="B11" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>64</v>
-      </c>
+      <c r="A12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
       <c r="F14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
+      <c r="A15" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="A16" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>42</v>
-      </c>
+      <c r="A19" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="20"/>
       <c r="C21" s="20"/>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
       <c r="F21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="20" t="s">
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="20" t="s">
+      <c r="B27" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-    </row>
-    <row r="32" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-    </row>
-    <row r="34" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" s="20" t="s">
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="27" t="s">
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
-      <c r="F41" s="24"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B46" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B47" s="27" t="s">
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B61" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
-      <c r="F47" s="24"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="28" t="s">
+      <c r="C61" s="23"/>
+      <c r="D61" s="23"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="23"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B62" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="23"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B63" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="B50" s="24"/>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-    </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B56" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B63" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="23"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
+      <c r="A64" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="23"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="23"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B67" s="20" t="s">
-        <v>110</v>
-      </c>
+      <c r="A65" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="23"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="20"/>
       <c r="C67" s="20"/>
       <c r="D67" s="20"/>
       <c r="E67" s="20"/>
       <c r="F67" s="20"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B68" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="B69" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="F70" s="26"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B72" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B73" s="20" t="s">
-        <v>124</v>
-      </c>
+      <c r="A68" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E68" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="F68" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="D69" s="24" t="n">
+        <v>226</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F69" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B70" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D70" s="26" t="n">
+        <v>263</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="F70" s="28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D71" s="26" t="n">
+        <v>263</v>
+      </c>
+      <c r="E71" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="B73" s="20"/>
       <c r="C73" s="20"/>
       <c r="D73" s="20"/>
       <c r="E73" s="20"/>
       <c r="F73" s="20"/>
     </row>
-    <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B74" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B75" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="B74" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
+      <c r="E75" s="23"/>
+      <c r="F75" s="23"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="B76" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25"/>
-    </row>
-    <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="B78" s="24"/>
-      <c r="C78" s="24"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B79" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-    </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="B80" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-    </row>
-    <row r="81" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="C81" s="24"/>
-      <c r="D81" s="24"/>
-      <c r="E81" s="24"/>
-      <c r="F81" s="24"/>
+      <c r="A76" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B76" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="F76" s="23"/>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23"/>
+      <c r="E77" s="23"/>
+      <c r="F77" s="23"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B80" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C80" s="23"/>
+      <c r="D80" s="23"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="23"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B81" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="C81" s="23"/>
+      <c r="D81" s="23"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="23"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" s="23"/>
+      <c r="D82" s="23"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="23"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="23"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B84" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84" s="23"/>
+      <c r="D84" s="23"/>
+      <c r="E84" s="23"/>
+      <c r="F84" s="23"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="C85" s="23"/>
+      <c r="D85" s="23"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="23"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B86" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="23"/>
+      <c r="D87" s="23"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="23"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="20"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="20"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="C91" s="22"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B92" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C93" s="22"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C94" s="22"/>
+      <c r="D94" s="22"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="C95" s="22"/>
+      <c r="D95" s="22"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="B96" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="C96" s="22"/>
+      <c r="D96" s="22"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="22"/>
+    </row>
+    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C97" s="22"/>
+      <c r="D97" s="22"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="22"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="B99" s="20"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="20"/>
+      <c r="E99" s="20"/>
+      <c r="F99" s="20"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="23"/>
+      <c r="D100" s="23"/>
+      <c r="E100" s="23"/>
+      <c r="F100" s="23"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="B101" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C101" s="23"/>
+      <c r="D101" s="23"/>
+      <c r="E101" s="23"/>
+      <c r="F101" s="23"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B102" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+      <c r="E102" s="23"/>
+      <c r="F102" s="23"/>
+    </row>
+    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B103" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C103" s="23"/>
+      <c r="D103" s="23"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="23"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B104" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="C104" s="23"/>
+      <c r="D104" s="23"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="23"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B105" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="C105" s="23"/>
+      <c r="D105" s="23"/>
+      <c r="E105" s="23"/>
+      <c r="F105" s="23"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B107" s="20"/>
+      <c r="C107" s="20"/>
+      <c r="D107" s="20"/>
+      <c r="E107" s="20"/>
+      <c r="F107" s="20"/>
+    </row>
+    <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="B108" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C108" s="23"/>
+      <c r="D108" s="23"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+    </row>
+    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B109" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="C109" s="23"/>
+      <c r="D109" s="23"/>
+      <c r="E109" s="23"/>
+      <c r="F109" s="23"/>
+    </row>
+    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B110" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="C110" s="23"/>
+      <c r="D110" s="23"/>
+      <c r="E110" s="23"/>
+      <c r="F110" s="23"/>
+    </row>
+    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="B111" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="23"/>
+    </row>
+    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B112" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="C112" s="23"/>
+      <c r="D112" s="23"/>
+      <c r="E112" s="23"/>
+      <c r="F112" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="94">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -3926,15 +4299,15 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B24:F24"/>
@@ -3942,12 +4315,13 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
@@ -3957,34 +4331,59 @@
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="A55:F55"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B57:F57"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="A60:F60"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B76:F76"/>
     <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B105:F105"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B112:F112"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4008,28 +4407,28 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>139</v>
+        <v>216</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>141</v>
+        <v>218</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>143</v>
+        <v>220</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>0</v>
@@ -4042,9 +4441,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>144</v>
+        <v>221</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0</v>
@@ -4057,9 +4456,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>145</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30" t="s">
+        <v>222</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">SUM(B4:B5)</f>
@@ -4074,20 +4473,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>147</v>
+        <v>224</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>149</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -4113,32 +4512,32 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>151</v>
+        <v>228</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>153</v>
+        <v>230</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>156</v>
+        <v>233</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4167,26 +4566,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>159</v>
+        <v>236</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>149</v>
+        <v>226</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4213,43 +4612,43 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>140</v>
+        <v>217</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>141</v>
+        <v>218</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>163</v>
+        <v>239</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>165</v>
+        <v>241</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>167</v>
+        <v>243</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>0</v>
@@ -4267,17 +4666,17 @@
       <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="30" t="n">
+      <c r="H4" s="31" t="n">
         <f aca="false">IFERROR(E4/D4,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>169</v>
+        <v>245</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -4295,17 +4694,17 @@
       <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="30" t="n">
+      <c r="H5" s="31" t="n">
         <f aca="false">IFERROR(E5/D5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
@@ -4323,17 +4722,17 @@
       <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="31" t="n">
         <f aca="false">IFERROR(E6/D6,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>174</v>
+        <v>250</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
@@ -4351,17 +4750,17 @@
       <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="31" t="n">
         <f aca="false">IFERROR(E7/D7,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0</v>
@@ -4379,17 +4778,17 @@
       <c r="G8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="31" t="n">
         <f aca="false">IFERROR(E8/D8,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>177</v>
+        <v>253</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>178</v>
+        <v>254</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -4407,14 +4806,14 @@
       <c r="G9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="30" t="n">
+      <c r="H9" s="31" t="n">
         <f aca="false">IFERROR(E9/D9,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>179</v>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="30" t="s">
+        <v>255</v>
       </c>
       <c r="C10" s="7" t="n">
         <f aca="false">SUM(C4:C9)</f>
@@ -4465,34 +4864,34 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>181</v>
+        <v>257</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>182</v>
+        <v>258</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>183</v>
+        <v>259</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>163</v>
+        <v>239</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>184</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="30" t="s">
+        <v>260</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>1</v>
@@ -4507,14 +4906,14 @@
         <f aca="false">C4-D4</f>
         <v>-2134.5</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="31" t="n">
         <f aca="false">IFERROR(D4/C4,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>185</v>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="30" t="s">
+        <v>261</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>0</v>
@@ -4529,14 +4928,14 @@
         <f aca="false">C5-D5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="31" t="n">
         <f aca="false">IFERROR(D5/C5,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>186</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="30" t="s">
+        <v>262</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>3</v>
@@ -4551,14 +4950,14 @@
         <f aca="false">C6-D6</f>
         <v>-113811.85</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="31" t="n">
         <f aca="false">IFERROR(D6/C6,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>187</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="s">
+        <v>263</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>2</v>
@@ -4573,16 +4972,16 @@
         <f aca="false">C7-D7</f>
         <v>-1215.62</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="31" t="n">
         <f aca="false">IFERROR(D7/C7,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="31" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="32" t="n">
         <f aca="false">SUM(B4:B7)</f>
         <v>6</v>
       </c>
@@ -4629,45 +5028,45 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="32" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="33" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>141</v>
+        <v>218</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>163</v>
+        <v>239</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>164</v>
+        <v>240</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>167</v>
+        <v>243</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
@@ -4679,21 +5078,21 @@
         <f aca="false">C5-D5</f>
         <v>-2134.5</v>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="31" t="n">
         <f aca="false">IFERROR((D5-C5)/C5,0)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="33" t="str">
+      <c r="G5" s="34" t="str">
         <f aca="false">IF(C5=0,"UNBUDGETED",IF(F5&gt;0.5,"CRITICAL",IF(F5&gt;0.1,"OVER",IF(F5&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>169</v>
+        <v>245</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>170</v>
+        <v>246</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>0</v>
@@ -4705,21 +5104,21 @@
         <f aca="false">C6-D6</f>
         <v>-106487.5</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="31" t="n">
         <f aca="false">IFERROR((D6-C6)/C6,0)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="33" t="str">
+      <c r="G6" s="34" t="str">
         <f aca="false">IF(C6=0,"UNBUDGETED",IF(F6&gt;0.5,"CRITICAL",IF(F6&gt;0.1,"OVER",IF(F6&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>0</v>
@@ -4731,21 +5130,21 @@
         <f aca="false">C7-D7</f>
         <v>-922.35</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="31" t="n">
         <f aca="false">IFERROR((D7-C7)/C7,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="33" t="str">
+      <c r="G7" s="34" t="str">
         <f aca="false">IF(C7=0,"UNBUDGETED",IF(F7&gt;0.5,"CRITICAL",IF(F7&gt;0.1,"OVER",IF(F7&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>174</v>
+        <v>250</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>0</v>
@@ -4757,21 +5156,21 @@
         <f aca="false">C8-D8</f>
         <v>-6402</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="31" t="n">
         <f aca="false">IFERROR((D8-C8)/C8,0)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="33" t="str">
+      <c r="G8" s="34" t="str">
         <f aca="false">IF(C8=0,"UNBUDGETED",IF(F8&gt;0.5,"CRITICAL",IF(F8&gt;0.1,"OVER",IF(F8&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -4783,21 +5182,21 @@
         <f aca="false">C9-D9</f>
         <v>-1052.32</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="31" t="n">
         <f aca="false">IFERROR((D9-C9)/C9,0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="33" t="str">
+      <c r="G9" s="34" t="str">
         <f aca="false">IF(C9=0,"UNBUDGETED",IF(F9&gt;0.5,"CRITICAL",IF(F9&gt;0.1,"OVER",IF(F9&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>177</v>
+        <v>253</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>178</v>
+        <v>254</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>0</v>
@@ -4809,11 +5208,11 @@
         <f aca="false">C10-D10</f>
         <v>-163.3</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="31" t="n">
         <f aca="false">IFERROR((D10-C10)/C10,0)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="33" t="str">
+      <c r="G10" s="34" t="str">
         <f aca="false">IF(C10=0,"UNBUDGETED",IF(F10&gt;0.5,"CRITICAL",IF(F10&gt;0.1,"OVER",IF(F10&lt;-0.1,"UNDER","ON"))))</f>
         <v>UNBUDGETED</v>
       </c>
@@ -4843,28 +5242,28 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="29" t="s">
-        <v>192</v>
+        <v>268</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>193</v>
+        <v>269</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>194</v>
+        <v>270</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>196</v>
+        <v>272</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>90628.75</v>
@@ -4872,14 +5271,14 @@
       <c r="C4" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="31" t="n">
         <f aca="false">IFERROR(B4/SUM(B$4:B$6),0)</f>
         <v>0.925225949969935</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>197</v>
+        <v>273</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>6402</v>
@@ -4887,14 +5286,14 @@
       <c r="C5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="31" t="n">
         <f aca="false">IFERROR(B5/SUM(B$4:B$6),0)</f>
         <v>0.0653578089922626</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>198</v>
+        <v>274</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>922.35</v>
@@ -4902,20 +5301,20 @@
       <c r="C6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="31" t="n">
         <f aca="false">IFERROR(B6/SUM(B$4:B$6),0)</f>
         <v>0.00941624103780279</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>199</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="s">
+        <v>275</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B4:B6)</f>
         <v>97953.1</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="35" t="n">
         <f aca="false">SUM(C4:C6)</f>
         <v>12</v>
       </c>
